--- a/project-template/报价单测试模板.xlsx
+++ b/project-template/报价单测试模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CarrotMRO\project-template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CarrotMRO\data\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8CD698-1B38-4FA6-8915-F874FED08B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12630C9-4068-4AC8-86AF-0713A2B00774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="940" windowWidth="14400" windowHeight="8273" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="11586" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>报价单</t>
   </si>
@@ -31,52 +31,65 @@
     <t>序号</t>
   </si>
   <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>{group.num}</t>
+  </si>
+  <si>
+    <t>=D{row}*E{row}</t>
+  </si>
+  <si>
+    <t>=SUM(F5:F{row-1})</t>
+  </si>
+  <si>
+    <t>税率</t>
+  </si>
+  <si>
+    <t>总价</t>
+  </si>
+  <si>
+    <t>=F{row-2}*(1+F{row-1})</t>
+  </si>
+  <si>
+    <t>总价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>项目名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>单位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{item.名称}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{item.单位}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{item.数量}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>单价</t>
-  </si>
-  <si>
-    <t>合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{item.单价}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{group.name}</t>
-  </si>
-  <si>
-    <t>{group.num}</t>
-  </si>
-  <si>
-    <t>{item.name}</t>
-  </si>
-  <si>
-    <t>{item.unit}</t>
-  </si>
-  <si>
-    <t>{item.quantity}</t>
-  </si>
-  <si>
-    <t>{item.unit_price}</t>
-  </si>
-  <si>
-    <t>=D{row}*E{row}</t>
-  </si>
-  <si>
-    <t>=SUM(F5:F{row-1})</t>
-  </si>
-  <si>
-    <t>税率</t>
-  </si>
-  <si>
-    <t>总价</t>
-  </si>
-  <si>
-    <t>=F{row-2}*(1+F{row-1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -136,10 +149,6 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -148,6 +157,10 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -438,7 +451,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" x14ac:dyDescent="0.7">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -448,7 +461,7 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="28" x14ac:dyDescent="0.7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
@@ -470,49 +483,49 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="20.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="20.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20.7" x14ac:dyDescent="0.55000000000000004">
@@ -525,38 +538,38 @@
     </row>
     <row r="8" spans="1:6" ht="20.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="6" t="s">
-        <v>15</v>
+      <c r="F8" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="6" t="s">
-        <v>18</v>
+      <c r="F10" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
